--- a/matlab/results/posthoc_results.xlsx
+++ b/matlab/results/posthoc_results.xlsx
@@ -19,16 +19,16 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>Urun</t>
+    <t>Product</t>
   </si>
   <si>
-    <t>Kategori</t>
+    <t>Category</t>
   </si>
   <si>
-    <t>Satis_Kanali</t>
+    <t>Sales_Channel</t>
   </si>
   <si>
-    <t>Musteri_Tipi</t>
+    <t>Customer_Type</t>
   </si>
   <si>
     <t>Method</t>
@@ -73,28 +73,28 @@
     <t>USB-C Hub</t>
   </si>
   <si>
-    <t>Elektronik</t>
+    <t>Electronics</t>
   </si>
   <si>
-    <t>Kırtasiye</t>
+    <t>Furniture</t>
   </si>
   <si>
-    <t>Mobilya</t>
+    <t>Accessories</t>
   </si>
   <si>
-    <t>Aksesuar</t>
+    <t>Office Accessories</t>
   </si>
   <si>
-    <t>Mağaza</t>
+    <t>Online</t>
   </si>
   <si>
-    <t>Bayi</t>
+    <t>Dealer</t>
   </si>
   <si>
-    <t>Bireysel</t>
+    <t>Corporate</t>
   </si>
   <si>
-    <t>KOBI</t>
+    <t>Individual</t>
   </si>
   <si>
     <t>Group2</t>
@@ -103,13 +103,13 @@
     <t>Wireless Mouse</t>
   </si>
   <si>
-    <t>Ofis Aksesuarları</t>
+    <t>Stationery</t>
   </si>
   <si>
-    <t>Online</t>
+    <t>Store</t>
   </si>
   <si>
-    <t>Kurumsal</t>
+    <t>SME</t>
   </si>
   <si>
     <t>MeanDiff</t>
@@ -176,7 +176,7 @@
   <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
     <col min="2" max="2" width="13.5703125" customWidth="true"/>
     <col min="3" max="3" width="20" customWidth="true"/>
     <col min="4" max="4" width="20" customWidth="true"/>
@@ -2141,7 +2141,7 @@
         <v>19</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E68" s="0">
         <v>-2461.3289180074653</v>
@@ -2170,16 +2170,16 @@
         <v>20</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E69" s="0">
-        <v>-3707.9844791965561</v>
+        <v>3026.4967977941174</v>
       </c>
       <c r="F69" s="0">
-        <v>-4344.4183058625558</v>
+        <v>2387.3530339986128</v>
       </c>
       <c r="G69" s="0">
-        <v>-3071.5506525305564</v>
+        <v>3665.6405615896219</v>
       </c>
       <c r="H69" s="0">
         <v>0</v>
@@ -2196,19 +2196,19 @@
         <v>6</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E70" s="0">
-        <v>3026.4967977941174</v>
+        <v>3707.9844791965561</v>
       </c>
       <c r="F70" s="0">
-        <v>2387.3530339986128</v>
+        <v>3071.5506525305564</v>
       </c>
       <c r="G70" s="0">
-        <v>3665.6405615896219</v>
+        <v>4344.4183058625558</v>
       </c>
       <c r="H70" s="0">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>6</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E71" s="0">
         <v>-2433.2906483375955</v>
@@ -2257,7 +2257,7 @@
         <v>19</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E72" s="0">
         <v>1246.6555611890913</v>
@@ -2283,10 +2283,10 @@
         <v>6</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E73" s="0">
         <v>1274.6938308589608</v>
@@ -2298,7 +2298,7 @@
         <v>1894.975736942182</v>
       </c>
       <c r="H73" s="0">
-        <v>2.0569687489407786e-07</v>
+        <v>2.0569687489407788e-07</v>
       </c>
       <c r="I73" s="0" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>19</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E74" s="0">
         <v>565.16787978665218</v>
@@ -2341,22 +2341,22 @@
         <v>6</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E75" s="0">
-        <v>-681.48768140243908</v>
+        <v>681.48768140243908</v>
       </c>
       <c r="F75" s="0">
-        <v>-1210.6337302305833</v>
+        <v>152.34163257429486</v>
       </c>
       <c r="G75" s="0">
-        <v>-152.34163257429498</v>
+        <v>1210.6337302305833</v>
       </c>
       <c r="H75" s="0">
-        <v>0.0040487819373281938</v>
+        <v>0.0040487819373282155</v>
       </c>
       <c r="I75" s="0" t="b">
         <v>1</v>
@@ -2370,10 +2370,10 @@
         <v>6</v>
       </c>
       <c r="C76" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="0" t="s">
         <v>22</v>
-      </c>
-      <c r="D76" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="E76" s="0">
         <v>593.20614945652176</v>
@@ -2385,7 +2385,7 @@
         <v>1216.2682475560532</v>
       </c>
       <c r="H76" s="0">
-        <v>0.070860873872589755</v>
+        <v>0.070860873872589797</v>
       </c>
       <c r="I76" s="0" t="b">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>6</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>19</v>
@@ -2408,10 +2408,10 @@
         <v>28.038269669869578</v>
       </c>
       <c r="F77" s="0">
-        <v>-516.11234781510495</v>
+        <v>-516.11234781510507</v>
       </c>
       <c r="G77" s="0">
-        <v>572.18888715484411</v>
+        <v>572.18888715484422</v>
       </c>
       <c r="H77" s="0">
         <v>0.99991238153340534</v>
@@ -2434,13 +2434,13 @@
         <v>30</v>
       </c>
       <c r="E78" s="0">
-        <v>329.66984605687389</v>
+        <v>-329.66984605687389</v>
       </c>
       <c r="F78" s="0">
-        <v>3.1245711982651301</v>
+        <v>-656.21512091548266</v>
       </c>
       <c r="G78" s="0">
-        <v>656.21512091548266</v>
+        <v>-3.1245711982651301</v>
       </c>
       <c r="H78" s="0">
         <v>0.047229042308440286</v>
@@ -2460,7 +2460,7 @@
         <v>24</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E79" s="0">
         <v>-336.45368816213704</v>
@@ -2489,7 +2489,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E80" s="0">
         <v>-6.7838421052631475</v>
@@ -2518,16 +2518,16 @@
         <v>25</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E81" s="0">
-        <v>-761.38012251973646</v>
+        <v>761.38012251973646</v>
       </c>
       <c r="F81" s="0">
-        <v>-1172.567379235054</v>
+        <v>350.19286580441883</v>
       </c>
       <c r="G81" s="0">
-        <v>-350.19286580441883</v>
+        <v>1172.567379235054</v>
       </c>
       <c r="H81" s="0">
         <v>4.2408605466510788e-05</v>
@@ -2544,19 +2544,19 @@
         <v>6</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>31</v>
       </c>
       <c r="E82" s="0">
-        <v>-724.67452613704154</v>
+        <v>724.67452613704154</v>
       </c>
       <c r="F82" s="0">
-        <v>-1179.8698987726648</v>
+        <v>269.47915350141835</v>
       </c>
       <c r="G82" s="0">
-        <v>-269.47915350141835</v>
+        <v>1179.8698987726648</v>
       </c>
       <c r="H82" s="0">
         <v>0.00055863648271887425</v>
@@ -2573,10 +2573,10 @@
         <v>6</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E83" s="0">
         <v>-36.705596382694921</v>
@@ -2603,7 +2603,7 @@
   <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
     <col min="2" max="2" width="11.28515625" customWidth="true"/>
     <col min="3" max="3" width="20" customWidth="true"/>
     <col min="4" max="4" width="20" customWidth="true"/>
@@ -4565,10 +4565,10 @@
         <v>37</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E68" s="0">
         <v>412.89422057264056</v>
@@ -4597,7 +4597,7 @@
         <v>19</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E69" s="0">
         <v>347.40877675188136</v>
@@ -4626,16 +4626,16 @@
         <v>20</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E70" s="0">
-        <v>-568.17682926829275</v>
+        <v>568.17682926829275</v>
       </c>
       <c r="F70" s="0">
-        <v>-671.70764092628167</v>
+        <v>464.64601761030383</v>
       </c>
       <c r="G70" s="0">
-        <v>-464.64601761030383</v>
+        <v>671.70764092628167</v>
       </c>
       <c r="H70" s="0">
         <v>0</v>
@@ -4652,19 +4652,19 @@
         <v>37</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E71" s="0">
-        <v>-268.7580792682927</v>
+        <v>268.7580792682927</v>
       </c>
       <c r="F71" s="0">
-        <v>-354.83603054215808</v>
+        <v>182.68012799442732</v>
       </c>
       <c r="G71" s="0">
-        <v>-182.68012799442732</v>
+        <v>354.83603054215808</v>
       </c>
       <c r="H71" s="0">
         <v>0</v>
@@ -4681,10 +4681,10 @@
         <v>37</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E72" s="0">
         <v>299.41874999999999</v>
@@ -4713,7 +4713,7 @@
         <v>19</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E73" s="0">
         <v>-220.76805251641133</v>
@@ -4739,10 +4739,10 @@
         <v>37</v>
       </c>
       <c r="C74" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="0" t="s">
         <v>22</v>
-      </c>
-      <c r="D74" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="E74" s="0">
         <v>144.13614130434786</v>
@@ -4768,10 +4768,10 @@
         <v>37</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E75" s="0">
         <v>-155.28260869565213</v>
@@ -4800,7 +4800,7 @@
         <v>19</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E76" s="0">
         <v>78.650697483588658</v>
@@ -4826,7 +4826,7 @@
         <v>37</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>19</v>
@@ -4861,13 +4861,13 @@
         <v>30</v>
       </c>
       <c r="E78" s="0">
-        <v>30.233569298649627</v>
+        <v>-30.233569298649627</v>
       </c>
       <c r="F78" s="0">
-        <v>-16.568660666495411</v>
+        <v>-77.035799263794672</v>
       </c>
       <c r="G78" s="0">
-        <v>77.035799263794672</v>
+        <v>16.568660666495411</v>
       </c>
       <c r="H78" s="0">
         <v>0.32539456391789967</v>
@@ -4887,7 +4887,7 @@
         <v>24</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E79" s="0">
         <v>-31.040856748042359</v>
@@ -4916,7 +4916,7 @@
         <v>24</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E80" s="0">
         <v>-0.80728744939273156</v>
@@ -4945,16 +4945,16 @@
         <v>25</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E81" s="0">
-        <v>-115.84690889497978</v>
+        <v>115.84690889497978</v>
       </c>
       <c r="F81" s="0">
-        <v>-175.19884380004058</v>
+        <v>56.494973989918975</v>
       </c>
       <c r="G81" s="0">
-        <v>-56.494973989918975</v>
+        <v>175.19884380004058</v>
       </c>
       <c r="H81" s="0">
         <v>9.4614062180475855e-06</v>
@@ -4971,19 +4971,19 @@
         <v>37</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>31</v>
       </c>
       <c r="E82" s="0">
-        <v>-104.75349947221082</v>
+        <v>104.75349947221082</v>
       </c>
       <c r="F82" s="0">
-        <v>-170.45769065160633</v>
+        <v>39.049308292815311</v>
       </c>
       <c r="G82" s="0">
-        <v>-39.049308292815311</v>
+        <v>170.45769065160633</v>
       </c>
       <c r="H82" s="0">
         <v>0.00042223928320650472</v>
@@ -5000,10 +5000,10 @@
         <v>37</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E83" s="0">
         <v>-11.093409422768957</v>
